--- a/data/trans_orig/P6601-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6601-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>200743</t>
+          <t>199495</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>238204</t>
+          <t>239732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>152362</t>
+          <t>154206</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>177532</t>
+          <t>177679</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>363663</t>
+          <t>363209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>409266</t>
+          <t>410277</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71016</t>
+          <t>70921</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103519</t>
+          <t>105264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25947</t>
+          <t>24991</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47222</t>
+          <t>46140</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103465</t>
+          <t>103740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142265</t>
+          <t>142778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27260</t>
+          <t>27144</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51030</t>
+          <t>51079</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15099</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33202</t>
+          <t>34021</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59819</t>
+          <t>60688</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>24225</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13662</t>
+          <t>12713</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12846</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31432</t>
+          <t>31164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>196964</t>
+          <t>196002</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>224452</t>
+          <t>224609</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>188494</t>
+          <t>188352</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>209572</t>
+          <t>210107</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>392257</t>
+          <t>394032</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>426558</t>
+          <t>428049</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32116</t>
+          <t>32087</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56608</t>
+          <t>57496</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>16697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37432</t>
+          <t>35759</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54695</t>
+          <t>53913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85868</t>
+          <t>84449</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20371</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11341</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26652</t>
+          <t>26727</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12155</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104235</t>
+          <t>104508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140885</t>
+          <t>139563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19018</t>
+          <t>19073</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34529</t>
+          <t>34559</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127687</t>
+          <t>127907</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>167121</t>
+          <t>170256</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,89%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95930</t>
+          <t>94445</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130652</t>
+          <t>128977</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26483</t>
+          <t>26079</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>110240</t>
+          <t>111965</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>151712</t>
+          <t>149775</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83450</t>
+          <t>83689</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>116460</t>
+          <t>117097</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91461</t>
+          <t>91874</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128270</t>
+          <t>128780</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>36550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61951</t>
+          <t>62572</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>911</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38389</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65268</t>
+          <t>63611</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>286413</t>
+          <t>285059</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>339301</t>
+          <t>336733</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>199573</t>
+          <t>201312</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>233784</t>
+          <t>232522</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>498258</t>
+          <t>498640</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>563573</t>
+          <t>560021</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>136662</t>
+          <t>137207</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>182270</t>
+          <t>179721</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45294</t>
+          <t>46665</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73566</t>
+          <t>74051</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>190924</t>
+          <t>194472</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>245682</t>
+          <t>245982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>159033</t>
+          <t>158270</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>207312</t>
+          <t>205597</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15322</t>
+          <t>15165</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33913</t>
+          <t>33782</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>178481</t>
+          <t>178203</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>230321</t>
+          <t>231847</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46000</t>
+          <t>45238</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79125</t>
+          <t>75239</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52248</t>
+          <t>52587</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82289</t>
+          <t>83279</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>64666</t>
+          <t>65920</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>93408</t>
+          <t>93941</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>154175</t>
+          <t>153557</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>177886</t>
+          <t>177691</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>225460</t>
+          <t>225599</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>265655</t>
+          <t>266346</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,36%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37936</t>
+          <t>37648</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>63179</t>
+          <t>62846</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21183</t>
+          <t>21532</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41782</t>
+          <t>42417</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>64032</t>
+          <t>63647</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96417</t>
+          <t>97785</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33908</t>
+          <t>33730</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58727</t>
+          <t>58027</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17136</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>41120</t>
+          <t>42141</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>69605</t>
+          <t>69566</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19188</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>24367</t>
+          <t>24438</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>902153</t>
+          <t>900998</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>988328</t>
+          <t>987789</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>749087</t>
+          <t>752301</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>804365</t>
+          <t>807122</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1667721</t>
+          <t>1672726</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1781254</t>
+          <t>1775756</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,68%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>410560</t>
+          <t>410023</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>483973</t>
+          <t>485242</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>147116</t>
+          <t>145802</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>193432</t>
+          <t>192637</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>574013</t>
+          <t>573042</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>664476</t>
+          <t>664309</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>337996</t>
+          <t>340265</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>408921</t>
+          <t>412300</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>39795</t>
+          <t>40726</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>69630</t>
+          <t>70374</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>392800</t>
+          <t>391170</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>470797</t>
+          <t>470899</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>115131</t>
+          <t>112030</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>158936</t>
+          <t>158264</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>33900</t>
+          <t>34220</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>136150</t>
+          <t>131274</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>184228</t>
+          <t>183164</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>136873</t>
+          <t>136375</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>174864</t>
+          <t>172029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79812</t>
+          <t>80438</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109586</t>
+          <t>110397</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>225781</t>
+          <t>229392</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>274045</t>
+          <t>272462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72268</t>
+          <t>73023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106798</t>
+          <t>107846</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56360</t>
+          <t>56485</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86714</t>
+          <t>85999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136399</t>
+          <t>137568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>180869</t>
+          <t>181434</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33487</t>
+          <t>33537</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59671</t>
+          <t>60060</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27912</t>
+          <t>27559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49197</t>
+          <t>48946</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78916</t>
+          <t>80364</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -4719,12 +4719,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25607</t>
+          <t>24531</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18510</t>
+          <t>17767</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37965</t>
+          <t>36722</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>136183</t>
+          <t>134789</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>168974</t>
+          <t>169035</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>106172</t>
+          <t>107590</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>131094</t>
+          <t>130499</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>249804</t>
+          <t>249826</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>292233</t>
+          <t>293264</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61570</t>
+          <t>61608</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93000</t>
+          <t>92091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27779</t>
+          <t>28167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49729</t>
+          <t>49582</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95993</t>
+          <t>97146</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134176</t>
+          <t>134924</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14977</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>33403</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15320</t>
+          <t>16187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20438</t>
+          <t>20673</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43516</t>
+          <t>42528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16704</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86321</t>
+          <t>84801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117764</t>
+          <t>118093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49932</t>
+          <t>50819</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70950</t>
+          <t>71029</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144653</t>
+          <t>145765</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182606</t>
+          <t>184094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>47,04%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74203</t>
+          <t>75717</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>105140</t>
+          <t>107451</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22178</t>
+          <t>22131</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41642</t>
+          <t>40839</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>102919</t>
+          <t>103525</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>140291</t>
+          <t>138502</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43318</t>
+          <t>44497</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69871</t>
+          <t>70819</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18278</t>
+          <t>18464</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55219</t>
+          <t>53115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84866</t>
+          <t>83164</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20767</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41827</t>
+          <t>43243</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16651</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28529</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53474</t>
+          <t>53117</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>141151</t>
+          <t>140641</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>179980</t>
+          <t>182576</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>145314</t>
+          <t>144812</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>181552</t>
+          <t>181238</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>298809</t>
+          <t>296813</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>354129</t>
+          <t>353201</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,73%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>108492</t>
+          <t>109276</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149007</t>
+          <t>147991</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78056</t>
+          <t>76684</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110865</t>
+          <t>111127</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196276</t>
+          <t>197319</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>247381</t>
+          <t>250004</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75746</t>
+          <t>76402</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>110842</t>
+          <t>110045</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17228</t>
+          <t>17344</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38236</t>
+          <t>37857</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>99981</t>
+          <t>99019</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>141297</t>
+          <t>138291</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31344</t>
+          <t>31471</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58071</t>
+          <t>58637</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>27264</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45799</t>
+          <t>46014</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77607</t>
+          <t>76674</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47766</t>
+          <t>47968</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>74769</t>
+          <t>73024</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>110469</t>
+          <t>111702</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>136234</t>
+          <t>136518</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>165946</t>
+          <t>164567</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>203229</t>
+          <t>203241</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,87%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>34306</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61642</t>
+          <t>59845</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29719</t>
+          <t>28787</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53532</t>
+          <t>52956</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72685</t>
+          <t>71959</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>104977</t>
+          <t>106011</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25478</t>
+          <t>24229</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46305</t>
+          <t>46780</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14806</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30830</t>
+          <t>30712</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>56934</t>
+          <t>56557</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20367</t>
+          <t>19875</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>591739</t>
+          <t>589661</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>667742</t>
+          <t>669063</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>530004</t>
+          <t>531326</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>594378</t>
+          <t>592947</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1146174</t>
+          <t>1144741</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1249935</t>
+          <t>1246569</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,68%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>396439</t>
+          <t>390243</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>464727</t>
+          <t>464612</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>245932</t>
+          <t>244687</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>304172</t>
+          <t>301053</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>657114</t>
+          <t>651151</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>748090</t>
+          <t>749621</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>225440</t>
+          <t>223220</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>287031</t>
+          <t>287165</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>55300</t>
+          <t>55040</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>88292</t>
+          <t>88803</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>290409</t>
+          <t>288561</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>356099</t>
+          <t>358542</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>84054</t>
+          <t>83222</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>128260</t>
+          <t>127030</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>56233</t>
+          <t>56350</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>123764</t>
+          <t>124099</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>174750</t>
+          <t>172749</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -8027,12 +8027,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>135325</t>
+          <t>135641</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>170034</t>
+          <t>169462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>101887</t>
+          <t>102999</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132023</t>
+          <t>132302</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>248762</t>
+          <t>246791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>293255</t>
+          <t>290847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,31%</t>
         </is>
       </c>
     </row>
@@ -8140,12 +8140,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59703</t>
+          <t>60481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88059</t>
+          <t>90672</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47908</t>
+          <t>47153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74303</t>
+          <t>73982</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114996</t>
+          <t>115286</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155600</t>
+          <t>154965</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -8253,12 +8253,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25306</t>
+          <t>24702</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48567</t>
+          <t>49700</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37974</t>
+          <t>37314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47845</t>
+          <t>47323</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78943</t>
+          <t>78785</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8338,12 +8338,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -8366,12 +8366,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24609</t>
+          <t>23479</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20163</t>
+          <t>19174</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15964</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35756</t>
+          <t>35962</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -8596,12 +8596,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>133926</t>
+          <t>132920</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>163853</t>
+          <t>164904</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100825</t>
+          <t>101066</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126722</t>
+          <t>128087</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>243623</t>
+          <t>242436</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>283333</t>
+          <t>284438</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>66,06%</t>
         </is>
       </c>
     </row>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51132</t>
+          <t>49898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79418</t>
+          <t>78644</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45175</t>
+          <t>44383</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70441</t>
+          <t>70635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103386</t>
+          <t>102571</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141409</t>
+          <t>142484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -8822,12 +8822,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32538</t>
+          <t>31969</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21615</t>
+          <t>23084</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24528</t>
+          <t>24987</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48185</t>
+          <t>48059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8907,12 +8907,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -8935,12 +8935,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13744</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8950,82 +8950,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7590</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>9300</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>4414</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>18044</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>1,03%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>919</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7689</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>9300</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>4094</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>17199</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -9165,12 +9165,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63351</t>
+          <t>62452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90950</t>
+          <t>90318</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30180</t>
+          <t>29497</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46226</t>
+          <t>46502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100068</t>
+          <t>98043</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>133840</t>
+          <t>132931</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -9278,12 +9278,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61121</t>
+          <t>62253</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>89824</t>
+          <t>91170</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27503</t>
+          <t>27509</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>79027</t>
+          <t>77411</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>112311</t>
+          <t>112116</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -9391,12 +9391,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29880</t>
+          <t>29533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53040</t>
+          <t>52371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13665</t>
+          <t>12217</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34375</t>
+          <t>35818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60509</t>
+          <t>61068</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9504,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13656</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30142</t>
+          <t>30814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>14730</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34116</t>
+          <t>33802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9589,12 +9589,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -9734,12 +9734,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>122812</t>
+          <t>123053</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>161530</t>
+          <t>163595</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9749,12 +9749,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>148340</t>
+          <t>147931</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>188095</t>
+          <t>186704</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9784,12 +9784,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>280702</t>
+          <t>281807</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>336486</t>
+          <t>340162</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9819,12 +9819,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -9847,12 +9847,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>162368</t>
+          <t>164263</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>204782</t>
+          <t>205389</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>99752</t>
+          <t>101799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>136871</t>
+          <t>136199</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9897,12 +9897,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>274662</t>
+          <t>276744</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>331127</t>
+          <t>332529</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9932,12 +9932,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,06%</t>
         </is>
       </c>
     </row>
@@ -9960,12 +9960,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91230</t>
+          <t>89675</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>128233</t>
+          <t>128225</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,82 +9975,82 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>18,51%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>26,47%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>52225</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>39269</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>66869</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>14,23%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>18,22%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>160318</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>137181</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>182843</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
           <t>18,83%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>26,47%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>52225</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>39892</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>66476</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>14,23%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>18,12%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>160318</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>137443</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>184732</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>18,83%</t>
-        </is>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -10073,12 +10073,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36784</t>
+          <t>36635</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64727</t>
+          <t>64686</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20280</t>
+          <t>20822</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42418</t>
+          <t>42104</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63133</t>
+          <t>62874</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97958</t>
+          <t>100265</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55865</t>
+          <t>53495</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>83041</t>
+          <t>81544</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>108590</t>
+          <t>108154</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>135923</t>
+          <t>134932</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>171486</t>
+          <t>171815</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>210417</t>
+          <t>211653</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,44%</t>
         </is>
       </c>
     </row>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63293</t>
+          <t>63186</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90299</t>
+          <t>91989</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10431,12 +10431,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>42215</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66380</t>
+          <t>67149</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10466,12 +10466,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>112555</t>
+          <t>112119</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>149893</t>
+          <t>150618</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -10529,12 +10529,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23280</t>
+          <t>23173</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44771</t>
+          <t>43354</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10544,12 +10544,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10579,12 +10579,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33667</t>
+          <t>35081</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>60295</t>
+          <t>61252</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -10642,12 +10642,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>24432</t>
+          <t>23914</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,12 +10657,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>12992</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>31030</t>
+          <t>31068</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>548910</t>
+          <t>551362</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>627082</t>
+          <t>624785</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>528856</t>
+          <t>528166</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>594341</t>
+          <t>593961</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1099098</t>
+          <t>1097171</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1199865</t>
+          <t>1196069</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,02%</t>
         </is>
       </c>
     </row>
@@ -10985,12 +10985,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>438564</t>
+          <t>438987</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>511772</t>
+          <t>510360</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11000,12 +11000,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>280099</t>
+          <t>280018</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>341143</t>
+          <t>341712</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>738978</t>
+          <t>736211</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>829941</t>
+          <t>833304</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11070,12 +11070,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -11098,12 +11098,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>210538</t>
+          <t>209032</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>270349</t>
+          <t>265719</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11113,12 +11113,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>94945</t>
+          <t>95023</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>133195</t>
+          <t>134845</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>318122</t>
+          <t>317022</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>387183</t>
+          <t>388376</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -11211,12 +11211,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>87609</t>
+          <t>88936</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>128215</t>
+          <t>127762</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11226,12 +11226,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39058</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>67899</t>
+          <t>66526</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11261,12 +11261,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>131973</t>
+          <t>131120</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>182300</t>
+          <t>181677</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11296,12 +11296,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -11669,32 +11669,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>106303</t>
+          <t>120007</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91984</t>
+          <t>105812</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120018</t>
+          <t>134695</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11704,32 +11704,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>92687</t>
+          <t>98582</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82141</t>
+          <t>87143</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102701</t>
+          <t>109020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11739,32 +11739,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>198991</t>
+          <t>218590</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>182927</t>
+          <t>200989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>216714</t>
+          <t>236447</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,5%</t>
         </is>
       </c>
     </row>
@@ -11782,32 +11782,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50696</t>
+          <t>53438</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37900</t>
+          <t>40513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64354</t>
+          <t>68520</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11817,32 +11817,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40599</t>
+          <t>43344</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31201</t>
+          <t>35369</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50109</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11852,32 +11852,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>91296</t>
+          <t>96783</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76491</t>
+          <t>80404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106891</t>
+          <t>114753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -11895,32 +11895,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15319</t>
+          <t>16234</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8920</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25250</t>
+          <t>25685</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11930,32 +11930,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12937</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11965,32 +11965,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>22830</t>
+          <t>24658</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14753</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33146</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -12008,32 +12008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>10287</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16576</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12043,32 +12043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9819</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>17464</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12078,32 +12078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10705</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26582</t>
+          <t>32837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -12121,17 +12121,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12156,17 +12156,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12238,32 +12238,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>100584</t>
+          <t>104254</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86403</t>
+          <t>90194</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>113787</t>
+          <t>117720</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12273,32 +12273,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77571</t>
+          <t>84007</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68386</t>
+          <t>73273</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86363</t>
+          <t>92447</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12308,32 +12308,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>178155</t>
+          <t>188262</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>162921</t>
+          <t>172155</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>194008</t>
+          <t>205682</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,56%</t>
         </is>
       </c>
     </row>
@@ -12351,32 +12351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>52696</t>
+          <t>55323</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40277</t>
+          <t>43851</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66654</t>
+          <t>69873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12386,32 +12386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30525</t>
+          <t>32696</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>24487</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39389</t>
+          <t>41917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12421,22 +12421,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>83222</t>
+          <t>88019</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69452</t>
+          <t>73364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99867</t>
+          <t>104445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -12464,7 +12464,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>812</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -12474,12 +12474,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12499,32 +12499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12534,32 +12534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>10133</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -12577,32 +12577,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15836</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12612,32 +12612,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12647,32 +12647,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19421</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -12690,17 +12690,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12725,17 +12725,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12760,17 +12760,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12807,32 +12807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>283730</t>
+          <t>43629</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102479</t>
+          <t>32754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348652</t>
+          <t>58220</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12842,32 +12842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>26859</t>
+          <t>30381</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20762</t>
+          <t>23565</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32379</t>
+          <t>35896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12877,32 +12877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>310589</t>
+          <t>74011</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150084</t>
+          <t>60731</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>388236</t>
+          <t>90331</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -12920,32 +12920,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54459</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>48336</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>170870</t>
+          <t>74384</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12955,32 +12955,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16022</t>
+          <t>18341</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12990,32 +12990,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>65172</t>
+          <t>73514</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16010</t>
+          <t>59308</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>165972</t>
+          <t>89534</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -13033,32 +13033,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>16759</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78861</t>
+          <t>36246</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13068,32 +13068,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13103,32 +13103,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>28412</t>
+          <t>30474</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>20202</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75423</t>
+          <t>41968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -13146,32 +13146,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39079</t>
+          <t>20603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13181,32 +13181,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13216,32 +13216,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>13785</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35653</t>
+          <t>24213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -13259,17 +13259,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13294,17 +13294,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13329,17 +13329,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13376,32 +13376,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>76280</t>
+          <t>87303</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59914</t>
+          <t>70738</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93032</t>
+          <t>106231</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13411,32 +13411,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>82645</t>
+          <t>89322</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70356</t>
+          <t>76905</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94366</t>
+          <t>102272</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13446,32 +13446,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>158925</t>
+          <t>176625</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>138358</t>
+          <t>155606</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>179204</t>
+          <t>201754</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -13489,32 +13489,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>124943</t>
+          <t>136272</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>107969</t>
+          <t>117775</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>141616</t>
+          <t>156321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13524,32 +13524,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>83695</t>
+          <t>94673</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71809</t>
+          <t>82664</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>96110</t>
+          <t>108199</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13559,32 +13559,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>208638</t>
+          <t>230944</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>188728</t>
+          <t>208158</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>232108</t>
+          <t>253605</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -13602,32 +13602,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42640</t>
+          <t>49668</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29159</t>
+          <t>36425</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57022</t>
+          <t>65004</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13637,32 +13637,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19474</t>
+          <t>22459</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13380</t>
+          <t>14616</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28006</t>
+          <t>32323</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13672,32 +13672,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>62114</t>
+          <t>72127</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>48266</t>
+          <t>55825</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>80097</t>
+          <t>90098</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -13715,32 +13715,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>16831</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>29200</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13750,32 +13750,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>15475</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20005</t>
+          <t>25634</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13785,32 +13785,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>27505</t>
+          <t>32306</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18997</t>
+          <t>20958</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41705</t>
+          <t>46210</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -13828,17 +13828,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13863,17 +13863,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13898,17 +13898,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>457182</t>
+          <t>512002</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>457182</t>
+          <t>512002</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>457182</t>
+          <t>512002</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13945,32 +13945,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40520</t>
+          <t>59210</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28880</t>
+          <t>44526</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54086</t>
+          <t>76006</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13980,32 +13980,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>100653</t>
+          <t>80755</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>81091</t>
+          <t>70394</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>129836</t>
+          <t>91724</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14015,32 +14015,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>141173</t>
+          <t>139965</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>114090</t>
+          <t>122489</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>192720</t>
+          <t>159231</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>49,24%</t>
         </is>
       </c>
     </row>
@@ -14058,32 +14058,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>71731</t>
+          <t>85346</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58925</t>
+          <t>69580</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85038</t>
+          <t>100287</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14093,32 +14093,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>55397</t>
+          <t>64106</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27775</t>
+          <t>53526</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73513</t>
+          <t>74338</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14128,32 +14128,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>127129</t>
+          <t>149452</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>86558</t>
+          <t>131915</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>151143</t>
+          <t>168290</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>52,04%</t>
         </is>
       </c>
     </row>
@@ -14171,32 +14171,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>14215</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24788</t>
+          <t>31078</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14206,32 +14206,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>16760</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14241,32 +14241,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>27034</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>40868</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -14284,32 +14284,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14319,7 +14319,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>829</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -14329,12 +14329,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14354,32 +14354,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>15465</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -14397,17 +14397,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14432,17 +14432,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14467,17 +14467,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14514,32 +14514,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>607418</t>
+          <t>414403</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>454823</t>
+          <t>380466</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>844621</t>
+          <t>451008</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14549,32 +14549,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>380417</t>
+          <t>383048</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>352913</t>
+          <t>357475</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>430736</t>
+          <t>406193</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14584,32 +14584,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>987834</t>
+          <t>797452</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>842891</t>
+          <t>750406</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1292817</t>
+          <t>834827</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>49,7%</t>
         </is>
       </c>
     </row>
@@ -14627,32 +14627,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>354526</t>
+          <t>392360</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>186029</t>
+          <t>355841</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>466991</t>
+          <t>426319</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14662,32 +14662,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>220930</t>
+          <t>246352</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>182131</t>
+          <t>223589</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>245221</t>
+          <t>267387</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14697,32 +14697,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>575456</t>
+          <t>638711</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>356397</t>
+          <t>598532</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>685083</t>
+          <t>679670</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -14740,69 +14740,69 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>96697</t>
+          <t>110165</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>47875</t>
+          <t>87295</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>134446</t>
+          <t>133668</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>13,81%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>48360</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>36267</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>62370</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
           <t>8,76%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>12,19%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>41164</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>29851</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>53384</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>151</t>
@@ -14810,32 +14810,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>137861</t>
+          <t>158525</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>83886</t>
+          <t>135838</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>172962</t>
+          <t>185396</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -14853,32 +14853,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>44600</t>
+          <t>50835</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>22548</t>
+          <t>36761</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>67706</t>
+          <t>71924</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14888,32 +14888,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>34102</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20958</t>
+          <t>24295</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41151</t>
+          <t>47508</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14923,32 +14923,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>74788</t>
+          <t>84937</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>44985</t>
+          <t>64875</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>97228</t>
+          <t>105415</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -14966,17 +14966,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15001,17 +15001,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15036,17 +15036,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1775939</t>
+          <t>1679625</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1775939</t>
+          <t>1679625</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1775939</t>
+          <t>1679625</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
